--- a/server/seed/Product_Database.xlsx
+++ b/server/seed/Product_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maelectricals.sharepoint.com/sites/ProjectCoordination/Shared Documents/MAE/Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="135" documentId="8_{EBC7D351-0979-4006-A801-EAB119450C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C23EAFB1-679D-48C1-8D1A-B0F2E741DDF9}"/>
+  <xr:revisionPtr revIDLastSave="138" documentId="8_{EBC7D351-0979-4006-A801-EAB119450C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6FF4B0C-894F-4161-8DA2-1567ED888C5E}"/>
   <bookViews>
-    <workbookView xWindow="1872" yWindow="5436" windowWidth="17280" windowHeight="8880" xr2:uid="{21F85595-19D1-4714-85EF-8F93F70DCA98}"/>
+    <workbookView xWindow="684" yWindow="828" windowWidth="17280" windowHeight="8880" xr2:uid="{21F85595-19D1-4714-85EF-8F93F70DCA98}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2893,6 +2893,9 @@
       <c r="E3" t="s">
         <v>32</v>
       </c>
+      <c r="G3">
+        <v>100</v>
+      </c>
       <c r="H3" t="s">
         <v>567</v>
       </c>
@@ -2925,6 +2928,9 @@
       <c r="E4" t="s">
         <v>31</v>
       </c>
+      <c r="G4">
+        <v>100</v>
+      </c>
       <c r="H4" t="s">
         <v>567</v>
       </c>
@@ -2956,6 +2962,9 @@
       </c>
       <c r="E5" t="s">
         <v>30</v>
+      </c>
+      <c r="G5">
+        <v>100</v>
       </c>
       <c r="H5" t="s">
         <v>567</v>
@@ -9137,7 +9146,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9797926-4691-4A32-A7E1-8BC3F4183B15}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9797926-4691-4A32-A7E1-8BC3F4183B15}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="5032d0b3-1e0e-4943-a888-fd7360781fc5"/>
+    <ds:schemaRef ds:uri="d10c95b8-36b2-487f-b11e-2c8a90c74a0d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/server/seed/Product_Database.xlsx
+++ b/server/seed/Product_Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maelectricals.sharepoint.com/sites/ProjectCoordination/Shared Documents/MAE/Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="138" documentId="8_{EBC7D351-0979-4006-A801-EAB119450C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6FF4B0C-894F-4161-8DA2-1567ED888C5E}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="8_{EBC7D351-0979-4006-A801-EAB119450C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBE449E4-67C0-4675-97A5-B3766BFC9315}"/>
   <bookViews>
-    <workbookView xWindow="684" yWindow="828" windowWidth="17280" windowHeight="8880" xr2:uid="{21F85595-19D1-4714-85EF-8F93F70DCA98}"/>
+    <workbookView xWindow="11412" yWindow="492" windowWidth="12624" windowHeight="12240" xr2:uid="{21F85595-19D1-4714-85EF-8F93F70DCA98}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="756">
   <si>
     <t>Product Name</t>
   </si>
@@ -2292,6 +2292,18 @@
   </si>
   <si>
     <t>8536</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Acti9 xC60 MCB 4P, 63A, C-curve, 10kA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Acti9 xC60 MCB 4P, 63A, D-curve, 10kA</t>
+  </si>
+  <si>
+    <t>A9N4P63CIN</t>
+  </si>
+  <si>
+    <t>A9N4P63DIN</t>
   </si>
 </sst>
 </file>
@@ -2858,9 +2870,6 @@
       <c r="E2" t="s">
         <v>33</v>
       </c>
-      <c r="G2">
-        <v>100</v>
-      </c>
       <c r="H2" t="s">
         <v>567</v>
       </c>
@@ -2893,9 +2902,6 @@
       <c r="E3" t="s">
         <v>32</v>
       </c>
-      <c r="G3">
-        <v>100</v>
-      </c>
       <c r="H3" t="s">
         <v>567</v>
       </c>
@@ -2928,9 +2934,6 @@
       <c r="E4" t="s">
         <v>31</v>
       </c>
-      <c r="G4">
-        <v>100</v>
-      </c>
       <c r="H4" t="s">
         <v>567</v>
       </c>
@@ -2963,9 +2966,6 @@
       <c r="E5" t="s">
         <v>30</v>
       </c>
-      <c r="G5">
-        <v>100</v>
-      </c>
       <c r="H5" t="s">
         <v>567</v>
       </c>
@@ -6312,10 +6312,10 @@
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>672</v>
+        <v>752</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>325</v>
+        <v>754</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>10</v>
@@ -6344,10 +6344,10 @@
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>672</v>
+        <v>753</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>325</v>
+        <v>755</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>10</v>
@@ -8808,6 +8808,9 @@
       <c r="E217" t="s">
         <v>562</v>
       </c>
+      <c r="G217">
+        <v>1000</v>
+      </c>
       <c r="H217" t="s">
         <v>567</v>
       </c>
@@ -8831,6 +8834,9 @@
       <c r="E218" t="s">
         <v>563</v>
       </c>
+      <c r="G218">
+        <v>1000</v>
+      </c>
       <c r="H218" t="s">
         <v>567</v>
       </c>
@@ -8854,6 +8860,9 @@
       <c r="E219" t="s">
         <v>564</v>
       </c>
+      <c r="G219">
+        <v>1000</v>
+      </c>
       <c r="H219" t="s">
         <v>567</v>
       </c>
@@ -8877,6 +8886,9 @@
       <c r="E220" t="s">
         <v>565</v>
       </c>
+      <c r="G220">
+        <v>1000</v>
+      </c>
       <c r="H220" t="s">
         <v>567</v>
       </c>
@@ -8899,6 +8911,9 @@
       </c>
       <c r="E221" t="s">
         <v>566</v>
+      </c>
+      <c r="G221">
+        <v>1000</v>
       </c>
       <c r="H221" t="s">
         <v>567</v>
@@ -8929,17 +8944,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007CB076283BA1CB439FD59BA6543B0C0B" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f2d1a0c085776dcff054242da74efbc7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5032d0b3-1e0e-4943-a888-fd7360781fc5" xmlns:ns3="d10c95b8-36b2-487f-b11e-2c8a90c74a0d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b95ce63e0dca839b2a57be17852c5705" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007CB076283BA1CB439FD59BA6543B0C0B" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f0386eecef1848fbfe63d74f248aaeba">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5032d0b3-1e0e-4943-a888-fd7360781fc5" xmlns:ns3="d10c95b8-36b2-487f-b11e-2c8a90c74a0d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c9003dcf120faa2162b5f4cc78223e57" ns2:_="" ns3:_="">
     <xsd:import namespace="5032d0b3-1e0e-4943-a888-fd7360781fc5"/>
     <xsd:import namespace="d10c95b8-36b2-487f-b11e-2c8a90c74a0d"/>
     <xsd:element name="properties">
@@ -9126,6 +9132,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -9138,15 +9153,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A85F38A4-B723-452F-A1B1-F9FDDBCAD374}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9797926-4691-4A32-A7E1-8BC3F4183B15}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5318E4B1-26EC-47B6-BA64-76EC47F3E5BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -9160,6 +9167,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A85F38A4-B723-452F-A1B1-F9FDDBCAD374}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/server/seed/Product_Database.xlsx
+++ b/server/seed/Product_Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maelectricals.sharepoint.com/sites/ProjectCoordination/Shared Documents/MAE/Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="8_{EBC7D351-0979-4006-A801-EAB119450C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBE449E4-67C0-4675-97A5-B3766BFC9315}"/>
+  <xr:revisionPtr revIDLastSave="154" documentId="8_{EBC7D351-0979-4006-A801-EAB119450C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FD4AA0F-F821-48CA-8F35-BA2863B14155}"/>
   <bookViews>
-    <workbookView xWindow="11412" yWindow="492" windowWidth="12624" windowHeight="12240" xr2:uid="{21F85595-19D1-4714-85EF-8F93F70DCA98}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{21F85595-19D1-4714-85EF-8F93F70DCA98}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -8808,9 +8808,6 @@
       <c r="E217" t="s">
         <v>562</v>
       </c>
-      <c r="G217">
-        <v>1000</v>
-      </c>
       <c r="H217" t="s">
         <v>567</v>
       </c>
@@ -8834,9 +8831,6 @@
       <c r="E218" t="s">
         <v>563</v>
       </c>
-      <c r="G218">
-        <v>1000</v>
-      </c>
       <c r="H218" t="s">
         <v>567</v>
       </c>
@@ -8860,9 +8854,6 @@
       <c r="E219" t="s">
         <v>564</v>
       </c>
-      <c r="G219">
-        <v>1000</v>
-      </c>
       <c r="H219" t="s">
         <v>567</v>
       </c>
@@ -8886,9 +8877,6 @@
       <c r="E220" t="s">
         <v>565</v>
       </c>
-      <c r="G220">
-        <v>1000</v>
-      </c>
       <c r="H220" t="s">
         <v>567</v>
       </c>
@@ -8911,9 +8899,6 @@
       </c>
       <c r="E221" t="s">
         <v>566</v>
-      </c>
-      <c r="G221">
-        <v>1000</v>
       </c>
       <c r="H221" t="s">
         <v>567</v>
@@ -8944,8 +8929,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007CB076283BA1CB439FD59BA6543B0C0B" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f0386eecef1848fbfe63d74f248aaeba">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5032d0b3-1e0e-4943-a888-fd7360781fc5" xmlns:ns3="d10c95b8-36b2-487f-b11e-2c8a90c74a0d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c9003dcf120faa2162b5f4cc78223e57" ns2:_="" ns3:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007CB076283BA1CB439FD59BA6543B0C0B" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2e7a2baae44e6558cdd6d9d93736c00d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5032d0b3-1e0e-4943-a888-fd7360781fc5" xmlns:ns3="d10c95b8-36b2-487f-b11e-2c8a90c74a0d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ad4ba2399fea4ac75ccf9db586f4d281" ns2:_="" ns3:_="">
     <xsd:import namespace="5032d0b3-1e0e-4943-a888-fd7360781fc5"/>
     <xsd:import namespace="d10c95b8-36b2-487f-b11e-2c8a90c74a0d"/>
     <xsd:element name="properties">
@@ -9132,15 +9126,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -9153,30 +9138,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5318E4B1-26EC-47B6-BA64-76EC47F3E5BC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A85F38A4-B723-452F-A1B1-F9FDDBCAD374}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="5032d0b3-1e0e-4943-a888-fd7360781fc5"/>
-    <ds:schemaRef ds:uri="d10c95b8-36b2-487f-b11e-2c8a90c74a0d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A85F38A4-B723-452F-A1B1-F9FDDBCAD374}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFE2BC69-5154-4C3F-89D8-5B7A91DEAD7A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
